--- a/artfynd/A 1475-2025 artfynd.xlsx
+++ b/artfynd/A 1475-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112513348</v>
+        <v>112513345</v>
       </c>
       <c r="B2" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514078</v>
+        <v>514052</v>
       </c>
       <c r="R2" t="n">
-        <v>6638105</v>
+        <v>6638087</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112513347</v>
+        <v>112513346</v>
       </c>
       <c r="B3" t="n">
-        <v>90965</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514099</v>
+        <v>514064</v>
       </c>
       <c r="R3" t="n">
-        <v>6638125</v>
+        <v>6638119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,6 +894,228 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112513347</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klotenområdet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514099</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6638125</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112513348</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klotenområdet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514079</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6638105</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
